--- a/final/table/workbooks/SuppTable_S2_Genomic_heritability.xlsx
+++ b/final/table/workbooks/SuppTable_S2_Genomic_heritability.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="348">
   <si>
     <t xml:space="preserve">trial</t>
   </si>
@@ -591,97 +591,16 @@
     <t xml:space="preserve">Condition</t>
   </si>
   <si>
-    <t xml:space="preserve">FeatureType</t>
+    <t xml:space="preserve">N_species</t>
   </si>
   <si>
-    <t xml:space="preserve">Lipid</t>
+    <t xml:space="preserve">CI_lo</t>
   </si>
   <si>
-    <t xml:space="preserve">BroadClass</t>
+    <t xml:space="preserve">CI_hi</t>
   </si>
   <si>
-    <t xml:space="preserve">n_genotypes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_markers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">model_status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lipid class sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatty acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatty acid amide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatty acid amide derivative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatty acid derivative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acylethanolamine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other annotated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other glycerolipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other glycerophospholipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prenol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sphingolipid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steroid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terpenoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tetrapyrrole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitamin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alkaloid-like compound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DGTS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dicarboxylic acid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flavonoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lipid-like compound</t>
+    <t xml:space="preserve">NonZero</t>
   </si>
   <si>
     <t xml:space="preserve">n_species</t>
@@ -1048,6 +967,9 @@
   </si>
   <si>
     <t xml:space="preserve">dropped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_genotypes</t>
   </si>
   <si>
     <t xml:space="preserve">n_h2_nonzero</t>
@@ -9908,34 +9830,25 @@
         <v>190</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>191</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>192</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>193</v>
       </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>194</v>
-      </c>
-      <c r="G1" t="s">
-        <v>195</v>
-      </c>
-      <c r="H1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I1" t="s">
-        <v>197</v>
-      </c>
-      <c r="J1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="2">
@@ -9943,30 +9856,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2" t="s">
-        <v>10</v>
+        <v>119</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>389</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.555</v>
       </c>
       <c r="F2" t="n">
-        <v>351</v>
+        <v>0.252</v>
       </c>
       <c r="G2" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.000000000039289836356701</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0392844262810799</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.00000000100013771453062</v>
-      </c>
-      <c r="K2" t="s">
-        <v>200</v>
+        <v>0.893</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -9974,30 +9882,25 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
-      </c>
-      <c r="C3"/>
-      <c r="D3"/>
-      <c r="E3" t="s">
-        <v>175</v>
+        <v>68</v>
+      </c>
+      <c r="C3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D3" t="n">
+        <v>389</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.217</v>
       </c>
       <c r="F3" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.000000000190173423574611</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.190149579043968</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.00000000100012539780822</v>
-      </c>
-      <c r="K3" t="s">
-        <v>200</v>
+        <v>0.564</v>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -10005,30 +9908,25 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4" t="s">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>389</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.111</v>
       </c>
       <c r="F4" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0000000000211188802545246</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0211160209496111</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.00000000100013540826648</v>
-      </c>
-      <c r="K4" t="s">
-        <v>200</v>
+        <v>0.401</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -10036,30 +9934,25 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5"/>
-      <c r="E5" t="s">
-        <v>36</v>
+        <v>169</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>389</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.017</v>
       </c>
       <c r="F5" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0000000000309803941625288</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0309769101977255</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.00000000100011246873226</v>
-      </c>
-      <c r="K5" t="s">
-        <v>200</v>
+        <v>0.243</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -10067,30 +9960,25 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6"/>
-      <c r="D6"/>
-      <c r="E6" t="s">
-        <v>21</v>
+        <v>36</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>389</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0167618160626606</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.219318859538318</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0710003731562989</v>
-      </c>
-      <c r="K6" t="s">
-        <v>200</v>
+        <v>0.078</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -10098,30 +9986,25 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7" t="s">
-        <v>201</v>
+        <v>50</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>389</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.000000000228598551595927</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.226657796068228</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.00000000100856249081571</v>
-      </c>
-      <c r="K7" t="s">
-        <v>200</v>
+        <v>0.141</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -10129,30 +10012,25 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8"/>
-      <c r="E8" t="s">
-        <v>202</v>
+        <v>57</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" t="n">
+        <v>389</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.000390820804344121</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.0297101177306831</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0129836750402098</v>
-      </c>
-      <c r="K8" t="s">
-        <v>200</v>
+        <v>0.084</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -10160,30 +10038,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9" t="s">
-        <v>203</v>
+        <v>177</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>389</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.00259986690134266</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.221155683356184</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0116192286553357</v>
-      </c>
-      <c r="K9" t="s">
-        <v>200</v>
+        <v>0.106</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -10191,30 +10064,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10" t="s">
-        <v>204</v>
+        <v>114</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>389</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.000000000309845639252683</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.309762508678906</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.00000000100026836773825</v>
-      </c>
-      <c r="K10" t="s">
-        <v>200</v>
+        <v>0.133</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -10222,30 +10090,25 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11" t="s">
-        <v>177</v>
+        <v>117</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>389</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0000000000443016473111194</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.0442978503126301</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.00000000100008571418606</v>
-      </c>
-      <c r="K11" t="s">
-        <v>200</v>
+        <v>0.137</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -10253,30 +10116,25 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
-      </c>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12" t="s">
-        <v>44</v>
+        <v>175</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>389</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0000000000611976266664544</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0611756846574323</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.00000000100035867106229</v>
-      </c>
-      <c r="K12" t="s">
-        <v>200</v>
+        <v>0.167</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -10284,30 +10142,25 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>389</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0000000000165012521471324</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.0164928807360542</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.00000000100050757625078</v>
-      </c>
-      <c r="K13" t="s">
-        <v>200</v>
+        <v>0.101</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -10315,30 +10168,25 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14" t="s">
-        <v>205</v>
+        <v>24</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" t="n">
+        <v>389</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.000000000198767805242725</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.197963494730796</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.0000000010040629223759</v>
-      </c>
-      <c r="K14" t="s">
-        <v>200</v>
+        <v>0.104</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -10346,30 +10194,25 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15" t="s">
-        <v>206</v>
+        <v>44</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>389</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.0000481498859254628</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.041242559614722</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.00116611912238291</v>
-      </c>
-      <c r="K15" t="s">
-        <v>200</v>
+        <v>0.208</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -10377,30 +10220,25 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>199</v>
-      </c>
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16" t="s">
-        <v>207</v>
+        <v>121</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" t="n">
+        <v>389</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0000000000440684494326813</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0440627912939727</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.00000000100012840980946</v>
-      </c>
-      <c r="K16" t="s">
-        <v>200</v>
+        <v>0.125</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -10408,30 +10246,25 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>199</v>
-      </c>
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17" t="s">
-        <v>208</v>
+        <v>153</v>
+      </c>
+      <c r="C17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" t="n">
+        <v>389</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0000000000346839365680213</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.034681239334961</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.00000000100007777110695</v>
-      </c>
-      <c r="K17" t="s">
-        <v>200</v>
+        <v>0.164</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10439,433 +10272,363 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18" t="s">
-        <v>121</v>
+        <v>166</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>389</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.0000000000746251886488253</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.074618117283533</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.00000000100009476640416</v>
-      </c>
-      <c r="K18" t="s">
-        <v>200</v>
+        <v>0.141</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19" t="s">
-        <v>153</v>
+        <v>21</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>357</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.404</v>
       </c>
       <c r="F19" t="n">
-        <v>351</v>
+        <v>0.153</v>
       </c>
       <c r="G19" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.0000000000490132461047864</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.0490126274339397</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.00000000100001262168272</v>
-      </c>
-      <c r="K19" t="s">
-        <v>200</v>
+        <v>0.708</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20" t="s">
-        <v>166</v>
+        <v>169</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>357</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.382</v>
       </c>
       <c r="F20" t="n">
-        <v>351</v>
+        <v>0.167</v>
       </c>
       <c r="G20" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.0000000000399847483458117</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.0399820178184709</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.00000000100006829288521</v>
-      </c>
-      <c r="K20" t="s">
-        <v>200</v>
+        <v>0.657</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B21" t="s">
-        <v>199</v>
-      </c>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21" t="s">
-        <v>169</v>
+        <v>68</v>
+      </c>
+      <c r="C21" t="n">
+        <v>66</v>
+      </c>
+      <c r="D21" t="n">
+        <v>357</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.208</v>
       </c>
       <c r="F21" t="n">
-        <v>351</v>
+        <v>0.017</v>
       </c>
       <c r="G21" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.00000000021606081076107</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.216039680441886</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.00000000100009780658377</v>
-      </c>
-      <c r="K21" t="s">
-        <v>200</v>
+        <v>0.525</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
-        <v>199</v>
-      </c>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22" t="s">
-        <v>209</v>
+        <v>57</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="n">
+        <v>357</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.172</v>
       </c>
       <c r="F22" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0000000000667508342245622</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.066728158025129</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.00000000100033982854211</v>
-      </c>
-      <c r="K22" t="s">
-        <v>200</v>
+        <v>0.505</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>199</v>
-      </c>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23" t="s">
-        <v>210</v>
+        <v>44</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>357</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.133</v>
       </c>
       <c r="F23" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.000000000058900437372841</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.0588962768011664</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.00000000100007064135453</v>
-      </c>
-      <c r="K23" t="s">
-        <v>200</v>
+        <v>0.45</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>199</v>
-      </c>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24" t="s">
-        <v>57</v>
+        <v>153</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>357</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.133</v>
       </c>
       <c r="F24" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0000000000519548649474454</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.0519524344086235</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.00000000100004678292543</v>
-      </c>
-      <c r="K24" t="s">
-        <v>200</v>
+        <v>0.45</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
-      </c>
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25" t="s">
-        <v>211</v>
+        <v>50</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>357</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.131</v>
       </c>
       <c r="F25" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.000000000147348617426818</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.147341084733806</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.00000000100005112318583</v>
-      </c>
-      <c r="K25" t="s">
-        <v>200</v>
+        <v>0.437</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26" t="s">
-        <v>212</v>
+        <v>166</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>357</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.127</v>
       </c>
       <c r="F26" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0000000000420653507416239</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0420624392874599</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.00000000100006921643502</v>
-      </c>
-      <c r="K26" t="s">
-        <v>200</v>
+        <v>0.42</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27" t="s">
-        <v>213</v>
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>357</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.117</v>
       </c>
       <c r="F27" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.000000000217614388303787</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.21748612376507</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.00000000100058975864186</v>
-      </c>
-      <c r="K27" t="s">
-        <v>200</v>
+        <v>0.365</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28" t="s">
-        <v>68</v>
+        <v>121</v>
+      </c>
+      <c r="C28" t="n">
+        <v>38</v>
+      </c>
+      <c r="D28" t="n">
+        <v>357</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.101</v>
       </c>
       <c r="F28" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00291157222426762</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.0892167226857476</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.0316034528492192</v>
-      </c>
-      <c r="K28" t="s">
-        <v>200</v>
+        <v>0.454</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29" t="s">
-        <v>214</v>
+        <v>114</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>357</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.071</v>
       </c>
       <c r="F29" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.0000000000250048022804647</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.025004208342508</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.0000000010000237525197</v>
-      </c>
-      <c r="K29" t="s">
-        <v>200</v>
+        <v>0.348</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30" t="s">
-        <v>215</v>
+        <v>36</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>357</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.065</v>
       </c>
       <c r="F30" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00000000000750273905254105</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.00750139387825374</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.00000000100017932224398</v>
-      </c>
-      <c r="K30" t="s">
-        <v>200</v>
+        <v>0.331</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31" t="s">
-        <v>216</v>
+        <v>24</v>
+      </c>
+      <c r="C31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D31" t="n">
+        <v>357</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.033</v>
       </c>
       <c r="F31" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.0000000000460148104275167</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.0460065590375245</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.00000000100017935146948</v>
-      </c>
-      <c r="K31" t="s">
-        <v>200</v>
+        <v>0.304</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -10873,30 +10636,25 @@
         <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>199</v>
-      </c>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32" t="s">
-        <v>10</v>
+        <v>117</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>357</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.021</v>
       </c>
       <c r="F32" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.00127076410176321</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.0419669736045753</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.0293901616776061</v>
-      </c>
-      <c r="K32" t="s">
-        <v>200</v>
+        <v>0.313</v>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -10904,30 +10662,25 @@
         <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33" t="s">
-        <v>217</v>
+        <v>175</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>357</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.015</v>
       </c>
       <c r="F33" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00405980194189737</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.141742984778584</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0278444742601553</v>
-      </c>
-      <c r="K33" t="s">
-        <v>200</v>
+        <v>0.246</v>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -10935,30 +10688,25 @@
         <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
-      </c>
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34" t="s">
-        <v>175</v>
+        <v>177</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>357</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.007</v>
       </c>
       <c r="F34" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0519673869303913</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.412182035389186</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.11196262330929</v>
-      </c>
-      <c r="K34" t="s">
-        <v>200</v>
+        <v>0.249</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -10966,898 +10714,25 @@
         <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35" t="s">
-        <v>24</v>
+        <v>119</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>357</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>357</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.000215668523523461</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.0173920429846963</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.0122485266425896</v>
-      </c>
-      <c r="K35" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>189</v>
-      </c>
-      <c r="B36" t="s">
-        <v>199</v>
-      </c>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" t="n">
-        <v>357</v>
-      </c>
-      <c r="G36" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.000594470388527267</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.0346112392341714</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.0168856243745187</v>
-      </c>
-      <c r="K36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>189</v>
-      </c>
-      <c r="B37" t="s">
-        <v>199</v>
-      </c>
-      <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37" t="s">
-        <v>218</v>
-      </c>
-      <c r="F37" t="n">
-        <v>357</v>
-      </c>
-      <c r="G37" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.0050054138453757</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.0949157994877057</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.0500936055358981</v>
-      </c>
-      <c r="K37" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>189</v>
-      </c>
-      <c r="B38" t="s">
-        <v>199</v>
-      </c>
-      <c r="C38"/>
-      <c r="D38"/>
-      <c r="E38" t="s">
-        <v>219</v>
-      </c>
-      <c r="F38" t="n">
-        <v>357</v>
-      </c>
-      <c r="G38" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.584627658647713</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.684633192500188</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.460604814305101</v>
-      </c>
-      <c r="K38" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>189</v>
-      </c>
-      <c r="B39" t="s">
-        <v>199</v>
-      </c>
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39" t="s">
-        <v>21</v>
-      </c>
-      <c r="F39" t="n">
-        <v>357</v>
-      </c>
-      <c r="G39" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.016987188309337</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.252909987662272</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.0629394814828441</v>
-      </c>
-      <c r="K39" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>189</v>
-      </c>
-      <c r="B40" t="s">
-        <v>199</v>
-      </c>
-      <c r="C40"/>
-      <c r="D40"/>
-      <c r="E40" t="s">
-        <v>201</v>
-      </c>
-      <c r="F40" t="n">
-        <v>357</v>
-      </c>
-      <c r="G40" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00847279265117926</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.0876290685815586</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.0881647092209795</v>
-      </c>
-      <c r="K40" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>189</v>
-      </c>
-      <c r="B41" t="s">
-        <v>199</v>
-      </c>
-      <c r="C41"/>
-      <c r="D41"/>
-      <c r="E41" t="s">
-        <v>202</v>
-      </c>
-      <c r="F41" t="n">
-        <v>357</v>
-      </c>
-      <c r="G41" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.000525638518657615</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.0197513712912738</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.0259228813116303</v>
-      </c>
-      <c r="K41" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>189</v>
-      </c>
-      <c r="B42" t="s">
-        <v>199</v>
-      </c>
-      <c r="C42"/>
-      <c r="D42"/>
-      <c r="E42" t="s">
-        <v>204</v>
-      </c>
-      <c r="F42" t="n">
-        <v>357</v>
-      </c>
-      <c r="G42" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.0107290186207227</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.0806370323192346</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.117428941169554</v>
-      </c>
-      <c r="K42" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>189</v>
-      </c>
-      <c r="B43" t="s">
-        <v>199</v>
-      </c>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43" t="s">
-        <v>220</v>
-      </c>
-      <c r="F43" t="n">
-        <v>357</v>
-      </c>
-      <c r="G43" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.0123210480109947</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.0851816254108239</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.126366258263413</v>
-      </c>
-      <c r="K43" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>189</v>
-      </c>
-      <c r="B44" t="s">
-        <v>199</v>
-      </c>
-      <c r="C44"/>
-      <c r="D44"/>
-      <c r="E44" t="s">
-        <v>177</v>
-      </c>
-      <c r="F44" t="n">
-        <v>357</v>
-      </c>
-      <c r="G44" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.0000000000430565114207358</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.0430149383876751</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.0000000010009664779614</v>
-      </c>
-      <c r="K44" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>189</v>
-      </c>
-      <c r="B45" t="s">
-        <v>199</v>
-      </c>
-      <c r="C45"/>
-      <c r="D45"/>
-      <c r="E45" t="s">
-        <v>221</v>
-      </c>
-      <c r="F45" t="n">
-        <v>357</v>
-      </c>
-      <c r="G45" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.0411556141839882</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.28333469973048</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.126831564515779</v>
-      </c>
-      <c r="K45" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>189</v>
-      </c>
-      <c r="B46" t="s">
-        <v>199</v>
-      </c>
-      <c r="C46"/>
-      <c r="D46"/>
-      <c r="E46" t="s">
-        <v>44</v>
-      </c>
-      <c r="F46" t="n">
-        <v>357</v>
-      </c>
-      <c r="G46" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.00116728760592887</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.0298901517213714</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.0375847987217286</v>
-      </c>
-      <c r="K46" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>189</v>
-      </c>
-      <c r="B47" t="s">
-        <v>199</v>
-      </c>
-      <c r="C47"/>
-      <c r="D47"/>
-      <c r="E47" t="s">
-        <v>50</v>
-      </c>
-      <c r="F47" t="n">
-        <v>357</v>
-      </c>
-      <c r="G47" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.000914167897691772</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.0293254403577883</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.0302308115227023</v>
-      </c>
-      <c r="K47" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>189</v>
-      </c>
-      <c r="B48" t="s">
-        <v>199</v>
-      </c>
-      <c r="C48"/>
-      <c r="D48"/>
-      <c r="E48" t="s">
-        <v>205</v>
-      </c>
-      <c r="F48" t="n">
-        <v>357</v>
-      </c>
-      <c r="G48" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.00820833938969157</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.0904340530906199</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.0832131012163956</v>
-      </c>
-      <c r="K48" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>189</v>
-      </c>
-      <c r="B49" t="s">
-        <v>199</v>
-      </c>
-      <c r="C49"/>
-      <c r="D49"/>
-      <c r="E49" t="s">
-        <v>206</v>
-      </c>
-      <c r="F49" t="n">
-        <v>357</v>
-      </c>
-      <c r="G49" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.000122619807582969</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.0266200824523906</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.00458516893285299</v>
-      </c>
-      <c r="K49" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>189</v>
-      </c>
-      <c r="B50" t="s">
-        <v>199</v>
-      </c>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50" t="s">
-        <v>207</v>
-      </c>
-      <c r="F50" t="n">
-        <v>357</v>
-      </c>
-      <c r="G50" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.000889790692122209</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.0322152673427405</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.0268777868078399</v>
-      </c>
-      <c r="K50" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>189</v>
-      </c>
-      <c r="B51" t="s">
-        <v>199</v>
-      </c>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51" t="s">
-        <v>208</v>
-      </c>
-      <c r="F51" t="n">
-        <v>357</v>
-      </c>
-      <c r="G51" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.00261590010428439</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.0214857101947507</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.108536320678503</v>
-      </c>
-      <c r="K51" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>189</v>
-      </c>
-      <c r="B52" t="s">
-        <v>199</v>
-      </c>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52" t="s">
-        <v>119</v>
-      </c>
-      <c r="F52" t="n">
-        <v>357</v>
-      </c>
-      <c r="G52" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.000000000367602499364426</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.36739391734426</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.00000000100056773300403</v>
-      </c>
-      <c r="K52" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>189</v>
-      </c>
-      <c r="B53" t="s">
-        <v>199</v>
-      </c>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53" t="s">
-        <v>121</v>
-      </c>
-      <c r="F53" t="n">
-        <v>357</v>
-      </c>
-      <c r="G53" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.0000000000992748594577725</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.0989731081058748</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.00000000100304882061496</v>
-      </c>
-      <c r="K53" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>189</v>
-      </c>
-      <c r="B54" t="s">
-        <v>199</v>
-      </c>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54" t="s">
-        <v>153</v>
-      </c>
-      <c r="F54" t="n">
-        <v>357</v>
-      </c>
-      <c r="G54" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.00110992031327993</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.0477727625790326</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.022705797791931</v>
-      </c>
-      <c r="K54" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>189</v>
-      </c>
-      <c r="B55" t="s">
-        <v>199</v>
-      </c>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55" t="s">
-        <v>166</v>
-      </c>
-      <c r="F55" t="n">
-        <v>357</v>
-      </c>
-      <c r="G55" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.000723660794301494</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.0397079416162332</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.0178983950958357</v>
-      </c>
-      <c r="K55" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>189</v>
-      </c>
-      <c r="B56" t="s">
-        <v>199</v>
-      </c>
-      <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56" t="s">
-        <v>210</v>
-      </c>
-      <c r="F56" t="n">
-        <v>357</v>
-      </c>
-      <c r="G56" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.000000000337351623098128</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.337161801306025</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.00000000100056299810307</v>
-      </c>
-      <c r="K56" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>189</v>
-      </c>
-      <c r="B57" t="s">
-        <v>199</v>
-      </c>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F57" t="n">
-        <v>357</v>
-      </c>
-      <c r="G57" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.00379907235054165</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.0486660635279938</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.0724113697015303</v>
-      </c>
-      <c r="K57" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>189</v>
-      </c>
-      <c r="B58" t="s">
-        <v>199</v>
-      </c>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58" t="s">
-        <v>212</v>
-      </c>
-      <c r="F58" t="n">
-        <v>357</v>
-      </c>
-      <c r="G58" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.000405371827045241</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.0442993125665639</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.00906777069436578</v>
-      </c>
-      <c r="K58" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>189</v>
-      </c>
-      <c r="B59" t="s">
-        <v>199</v>
-      </c>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59" t="s">
-        <v>213</v>
-      </c>
-      <c r="F59" t="n">
-        <v>357</v>
-      </c>
-      <c r="G59" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.00299748702326928</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.11451120918161</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.025508639956681</v>
-      </c>
-      <c r="K59" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>189</v>
-      </c>
-      <c r="B60" t="s">
-        <v>199</v>
-      </c>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" t="n">
-        <v>357</v>
-      </c>
-      <c r="G60" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.00421080582388219</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.0590305375797266</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.0665831178981867</v>
-      </c>
-      <c r="K60" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>189</v>
-      </c>
-      <c r="B61" t="s">
-        <v>199</v>
-      </c>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61" t="s">
-        <v>214</v>
-      </c>
-      <c r="F61" t="n">
-        <v>357</v>
-      </c>
-      <c r="G61" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.0000000000408252710772969</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.0408219224484294</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.00000000100008202916076</v>
-      </c>
-      <c r="K61" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>189</v>
-      </c>
-      <c r="B62" t="s">
-        <v>199</v>
-      </c>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62" t="s">
-        <v>215</v>
-      </c>
-      <c r="F62" t="n">
-        <v>357</v>
-      </c>
-      <c r="G62" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.00025611270327895</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.0185158266463992</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.0136433800742778</v>
-      </c>
-      <c r="K62" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>189</v>
-      </c>
-      <c r="B63" t="s">
-        <v>199</v>
-      </c>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63" t="s">
-        <v>216</v>
-      </c>
-      <c r="F63" t="n">
-        <v>357</v>
-      </c>
-      <c r="G63" t="n">
-        <v>65486</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.0000000000695922122853305</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.0690528229283638</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.00000000100781125613634</v>
-      </c>
-      <c r="K63" t="s">
-        <v>200</v>
+        <v>0.123</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11879,7 +10754,7 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -11894,25 +10769,25 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="I1" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="J1" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="K1" t="s">
         <v>7</v>
       </c>
       <c r="L1" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="M1" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="N1" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2">
@@ -13081,22 +11956,22 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="G1" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="H1" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="I1" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="J1" t="s">
         <v>4</v>
@@ -13108,31 +11983,31 @@
         <v>6</v>
       </c>
       <c r="M1" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="N1" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="O1" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="P1" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="Q1" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="R1" t="s">
         <v>7</v>
       </c>
       <c r="S1" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="T1" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="U1" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2">
@@ -13143,7 +12018,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -13208,7 +12083,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -13273,7 +12148,7 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -13338,7 +12213,7 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -13403,7 +12278,7 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -13468,7 +12343,7 @@
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -13533,7 +12408,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -13598,7 +12473,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -13660,10 +12535,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -13728,7 +12603,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -13793,7 +12668,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -13858,7 +12733,7 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -13923,7 +12798,7 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
@@ -13985,10 +12860,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -14115,7 +12990,7 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
@@ -14180,7 +13055,7 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
         <v>24</v>
@@ -14440,7 +13315,7 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
@@ -14570,7 +13445,7 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
@@ -15610,7 +14485,7 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="C40" t="s">
         <v>44</v>
@@ -15675,7 +14550,7 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="C41" t="s">
         <v>44</v>
@@ -15935,7 +14810,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
@@ -16328,7 +15203,7 @@
         <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D51" t="b">
         <v>1</v>
@@ -16520,7 +15395,7 @@
         <v>8</v>
       </c>
       <c r="B54" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="C54" t="s">
         <v>57</v>
@@ -17365,7 +16240,7 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C67" t="s">
         <v>68</v>
@@ -17560,7 +16435,7 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="C70" t="s">
         <v>68</v>
@@ -17625,7 +16500,7 @@
         <v>8</v>
       </c>
       <c r="B71" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="C71" t="s">
         <v>68</v>
@@ -17690,7 +16565,7 @@
         <v>8</v>
       </c>
       <c r="B72" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="C72" t="s">
         <v>68</v>
@@ -17820,7 +16695,7 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="C74" t="s">
         <v>68</v>
@@ -18015,7 +16890,7 @@
         <v>8</v>
       </c>
       <c r="B77" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="C77" t="s">
         <v>68</v>
@@ -18145,7 +17020,7 @@
         <v>8</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="C79" t="s">
         <v>68</v>
@@ -18210,7 +17085,7 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="C80" t="s">
         <v>68</v>
@@ -18470,7 +17345,7 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="C84" t="s">
         <v>68</v>
@@ -18535,7 +17410,7 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="C85" t="s">
         <v>68</v>
@@ -19055,7 +17930,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="C93" t="s">
         <v>68</v>
@@ -19250,7 +18125,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="C96" t="s">
         <v>68</v>
@@ -19510,7 +18385,7 @@
         <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="C100" t="s">
         <v>68</v>
@@ -19705,7 +18580,7 @@
         <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="C103" t="s">
         <v>68</v>
@@ -19965,7 +18840,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="C107" t="s">
         <v>68</v>
@@ -20095,7 +18970,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="C109" t="s">
         <v>68</v>
@@ -20160,7 +19035,7 @@
         <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="C110" t="s">
         <v>68</v>
@@ -20290,7 +19165,7 @@
         <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="C112" t="s">
         <v>68</v>
@@ -20680,7 +19555,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -20745,7 +19620,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C119" t="s">
         <v>68</v>
@@ -20940,7 +19815,7 @@
         <v>8</v>
       </c>
       <c r="B122" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="C122" t="s">
         <v>68</v>
@@ -21200,7 +20075,7 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="C126" t="s">
         <v>68</v>
@@ -21330,7 +20205,7 @@
         <v>8</v>
       </c>
       <c r="B128" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="C128" t="s">
         <v>68</v>
@@ -21460,10 +20335,10 @@
         <v>8</v>
       </c>
       <c r="B130" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="C130" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D130" t="b">
         <v>0</v>
@@ -22110,7 +20985,7 @@
         <v>8</v>
       </c>
       <c r="B140" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="C140" t="s">
         <v>121</v>
@@ -23475,7 +22350,7 @@
         <v>8</v>
       </c>
       <c r="B161" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="C161" t="s">
         <v>121</v>
@@ -23865,7 +22740,7 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="C167" t="s">
         <v>121</v>
@@ -23930,7 +22805,7 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="C168" t="s">
         <v>121</v>
@@ -24060,7 +22935,7 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="C170" t="s">
         <v>114</v>
@@ -24190,7 +23065,7 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C172" t="s">
         <v>114</v>
@@ -24255,7 +23130,7 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="C173" t="s">
         <v>121</v>
@@ -24840,7 +23715,7 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="C182" t="s">
         <v>153</v>
@@ -24970,7 +23845,7 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="C184" t="s">
         <v>153</v>
@@ -25360,7 +24235,7 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="C190" t="s">
         <v>166</v>
@@ -25490,7 +24365,7 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="C192" t="s">
         <v>169</v>
@@ -25558,7 +24433,7 @@
         <v>170</v>
       </c>
       <c r="C193" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D193" t="b">
         <v>1</v>
@@ -25623,7 +24498,7 @@
         <v>171</v>
       </c>
       <c r="C194" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D194" t="b">
         <v>1</v>
@@ -25688,7 +24563,7 @@
         <v>172</v>
       </c>
       <c r="C195" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D195" t="b">
         <v>1</v>
@@ -25753,7 +24628,7 @@
         <v>173</v>
       </c>
       <c r="C196" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D196" t="b">
         <v>1</v>
@@ -25818,7 +24693,7 @@
         <v>174</v>
       </c>
       <c r="C197" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D197" t="b">
         <v>1</v>
@@ -25880,10 +24755,10 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="C198" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D198" t="b">
         <v>0</v>
@@ -25948,7 +24823,7 @@
         <v>176</v>
       </c>
       <c r="C199" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D199" t="b">
         <v>1</v>
@@ -26013,7 +24888,7 @@
         <v>178</v>
       </c>
       <c r="C200" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D200" t="b">
         <v>1</v>
@@ -26075,10 +24950,10 @@
         <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="C201" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D201" t="b">
         <v>0</v>
@@ -26140,10 +25015,10 @@
         <v>8</v>
       </c>
       <c r="B202" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D202" t="b">
         <v>0</v>
@@ -26208,7 +25083,7 @@
         <v>179</v>
       </c>
       <c r="C203" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D203" t="b">
         <v>1</v>
@@ -26273,7 +25148,7 @@
         <v>180</v>
       </c>
       <c r="C204" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D204" t="b">
         <v>1</v>
@@ -26338,7 +25213,7 @@
         <v>181</v>
       </c>
       <c r="C205" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D205" t="b">
         <v>1</v>
@@ -26400,10 +25275,10 @@
         <v>8</v>
       </c>
       <c r="B206" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="C206" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D206" t="b">
         <v>0</v>
@@ -26465,10 +25340,10 @@
         <v>8</v>
       </c>
       <c r="B207" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="C207" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D207" t="b">
         <v>0</v>
@@ -26533,7 +25408,7 @@
         <v>182</v>
       </c>
       <c r="C208" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D208" t="b">
         <v>1</v>
@@ -26595,10 +25470,10 @@
         <v>8</v>
       </c>
       <c r="B209" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="C209" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D209" t="b">
         <v>0</v>
@@ -26663,7 +25538,7 @@
         <v>183</v>
       </c>
       <c r="C210" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D210" t="b">
         <v>1</v>
@@ -26728,7 +25603,7 @@
         <v>184</v>
       </c>
       <c r="C211" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D211" t="b">
         <v>1</v>
@@ -26793,7 +25668,7 @@
         <v>185</v>
       </c>
       <c r="C212" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D212" t="b">
         <v>1</v>
@@ -26858,7 +25733,7 @@
         <v>186</v>
       </c>
       <c r="C213" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D213" t="b">
         <v>1</v>
@@ -26923,7 +25798,7 @@
         <v>187</v>
       </c>
       <c r="C214" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D214" t="b">
         <v>1</v>
@@ -26988,7 +25863,7 @@
         <v>188</v>
       </c>
       <c r="C215" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D215" t="b">
         <v>1</v>
@@ -27053,7 +25928,7 @@
         <v>181</v>
       </c>
       <c r="C216" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D216" t="b">
         <v>1</v>
@@ -27115,10 +25990,10 @@
         <v>189</v>
       </c>
       <c r="B217" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="C217" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D217" t="b">
         <v>0</v>
@@ -27183,7 +26058,7 @@
         <v>182</v>
       </c>
       <c r="C218" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D218" t="b">
         <v>1</v>
@@ -27248,7 +26123,7 @@
         <v>179</v>
       </c>
       <c r="C219" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D219" t="b">
         <v>1</v>
@@ -27313,7 +26188,7 @@
         <v>17</v>
       </c>
       <c r="C220" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D220" t="b">
         <v>1</v>
@@ -27375,10 +26250,10 @@
         <v>189</v>
       </c>
       <c r="B221" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="C221" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D221" t="b">
         <v>0</v>
@@ -27440,10 +26315,10 @@
         <v>189</v>
       </c>
       <c r="B222" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="C222" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D222" t="b">
         <v>0</v>
@@ -27505,10 +26380,10 @@
         <v>189</v>
       </c>
       <c r="B223" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="C223" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D223" t="b">
         <v>0</v>
@@ -27570,10 +26445,10 @@
         <v>189</v>
       </c>
       <c r="B224" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="C224" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D224" t="b">
         <v>0</v>
@@ -27638,7 +26513,7 @@
         <v>18</v>
       </c>
       <c r="C225" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D225" t="b">
         <v>1</v>
@@ -27703,7 +26578,7 @@
         <v>19</v>
       </c>
       <c r="C226" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D226" t="b">
         <v>1</v>
@@ -27768,7 +26643,7 @@
         <v>9</v>
       </c>
       <c r="C227" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D227" t="b">
         <v>1</v>
@@ -27833,7 +26708,7 @@
         <v>11</v>
       </c>
       <c r="C228" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D228" t="b">
         <v>1</v>
@@ -27898,7 +26773,7 @@
         <v>12</v>
       </c>
       <c r="C229" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D229" t="b">
         <v>1</v>
@@ -27963,7 +26838,7 @@
         <v>13</v>
       </c>
       <c r="C230" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D230" t="b">
         <v>1</v>
@@ -28028,7 +26903,7 @@
         <v>14</v>
       </c>
       <c r="C231" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D231" t="b">
         <v>1</v>
@@ -28093,7 +26968,7 @@
         <v>15</v>
       </c>
       <c r="C232" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D232" t="b">
         <v>1</v>
@@ -28158,7 +27033,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D233" t="b">
         <v>1</v>
@@ -28223,7 +27098,7 @@
         <v>170</v>
       </c>
       <c r="C234" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D234" t="b">
         <v>1</v>
@@ -28288,7 +27163,7 @@
         <v>183</v>
       </c>
       <c r="C235" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D235" t="b">
         <v>1</v>
@@ -28353,7 +27228,7 @@
         <v>184</v>
       </c>
       <c r="C236" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D236" t="b">
         <v>1</v>
@@ -28418,7 +27293,7 @@
         <v>185</v>
       </c>
       <c r="C237" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D237" t="b">
         <v>1</v>
@@ -28483,7 +27358,7 @@
         <v>174</v>
       </c>
       <c r="C238" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D238" t="b">
         <v>1</v>
@@ -28548,7 +27423,7 @@
         <v>186</v>
       </c>
       <c r="C239" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D239" t="b">
         <v>1</v>
@@ -28870,7 +27745,7 @@
         <v>189</v>
       </c>
       <c r="B244" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="C244" t="s">
         <v>24</v>
@@ -29065,7 +27940,7 @@
         <v>189</v>
       </c>
       <c r="B247" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="C247" t="s">
         <v>24</v>
@@ -29520,7 +28395,7 @@
         <v>189</v>
       </c>
       <c r="B254" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="C254" t="s">
         <v>24</v>
@@ -30040,10 +28915,10 @@
         <v>189</v>
       </c>
       <c r="B262" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="C262" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D262" t="b">
         <v>0</v>
@@ -30108,7 +28983,7 @@
         <v>20</v>
       </c>
       <c r="C263" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D263" t="b">
         <v>1</v>
@@ -30170,10 +29045,10 @@
         <v>189</v>
       </c>
       <c r="B264" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="C264" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D264" t="b">
         <v>0</v>
@@ -30238,7 +29113,7 @@
         <v>176</v>
       </c>
       <c r="C265" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D265" t="b">
         <v>1</v>
@@ -30303,7 +29178,7 @@
         <v>178</v>
       </c>
       <c r="C266" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D266" t="b">
         <v>1</v>
@@ -30368,7 +29243,7 @@
         <v>180</v>
       </c>
       <c r="C267" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D267" t="b">
         <v>1</v>
@@ -30433,7 +29308,7 @@
         <v>187</v>
       </c>
       <c r="C268" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D268" t="b">
         <v>1</v>
@@ -30495,10 +29370,10 @@
         <v>189</v>
       </c>
       <c r="B269" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="C269" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D269" t="b">
         <v>0</v>
@@ -30560,10 +29435,10 @@
         <v>189</v>
       </c>
       <c r="B270" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="C270" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D270" t="b">
         <v>0</v>
@@ -30690,7 +29565,7 @@
         <v>189</v>
       </c>
       <c r="B272" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="C272" t="s">
         <v>114</v>
@@ -30885,10 +29760,10 @@
         <v>189</v>
       </c>
       <c r="B275" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="C275" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D275" t="b">
         <v>0</v>
@@ -30953,7 +29828,7 @@
         <v>188</v>
       </c>
       <c r="C276" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D276" t="b">
         <v>1</v>
@@ -31015,10 +29890,10 @@
         <v>189</v>
       </c>
       <c r="B277" t="s">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="C277" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D277" t="b">
         <v>0</v>
@@ -31730,10 +30605,10 @@
         <v>189</v>
       </c>
       <c r="B288" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C288" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D288" t="b">
         <v>0</v>
@@ -31795,10 +30670,10 @@
         <v>189</v>
       </c>
       <c r="B289" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="C289" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D289" t="b">
         <v>0</v>
@@ -31860,10 +30735,10 @@
         <v>189</v>
       </c>
       <c r="B290" t="s">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="C290" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D290" t="b">
         <v>0</v>
@@ -31928,7 +30803,7 @@
         <v>22</v>
       </c>
       <c r="C291" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D291" t="b">
         <v>1</v>
@@ -31990,7 +30865,7 @@
         <v>189</v>
       </c>
       <c r="B292" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="C292" t="s">
         <v>119</v>
@@ -32123,7 +30998,7 @@
         <v>55</v>
       </c>
       <c r="C294" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D294" t="b">
         <v>1</v>
@@ -32900,7 +31775,7 @@
         <v>189</v>
       </c>
       <c r="B306" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="C306" t="s">
         <v>121</v>
@@ -33420,7 +32295,7 @@
         <v>189</v>
       </c>
       <c r="B314" t="s">
-        <v>309</v>
+        <v>282</v>
       </c>
       <c r="C314" t="s">
         <v>121</v>
@@ -33485,7 +32360,7 @@
         <v>189</v>
       </c>
       <c r="B315" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="C315" t="s">
         <v>121</v>
@@ -33550,7 +32425,7 @@
         <v>189</v>
       </c>
       <c r="B316" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="C316" t="s">
         <v>121</v>
@@ -34395,7 +33270,7 @@
         <v>189</v>
       </c>
       <c r="B329" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="C329" t="s">
         <v>121</v>
@@ -34525,7 +33400,7 @@
         <v>189</v>
       </c>
       <c r="B331" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="C331" t="s">
         <v>121</v>
@@ -34590,7 +33465,7 @@
         <v>189</v>
       </c>
       <c r="B332" t="s">
-        <v>314</v>
+        <v>287</v>
       </c>
       <c r="C332" t="s">
         <v>121</v>
@@ -35175,7 +34050,7 @@
         <v>189</v>
       </c>
       <c r="B341" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="C341" t="s">
         <v>153</v>
@@ -35305,7 +34180,7 @@
         <v>189</v>
       </c>
       <c r="B343" t="s">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="C343" t="s">
         <v>153</v>
@@ -35370,7 +34245,7 @@
         <v>189</v>
       </c>
       <c r="B344" t="s">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="C344" t="s">
         <v>153</v>
@@ -35695,7 +34570,7 @@
         <v>189</v>
       </c>
       <c r="B349" t="s">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="C349" t="s">
         <v>166</v>
@@ -36605,7 +35480,7 @@
         <v>189</v>
       </c>
       <c r="B363" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="C363" t="s">
         <v>68</v>
@@ -36735,7 +35610,7 @@
         <v>189</v>
       </c>
       <c r="B365" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="C365" t="s">
         <v>68</v>
@@ -37125,7 +36000,7 @@
         <v>189</v>
       </c>
       <c r="B371" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="C371" t="s">
         <v>68</v>
@@ -37580,7 +36455,7 @@
         <v>189</v>
       </c>
       <c r="B378" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="C378" t="s">
         <v>68</v>
@@ -37710,7 +36585,7 @@
         <v>189</v>
       </c>
       <c r="B380" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="C380" t="s">
         <v>68</v>
@@ -37775,7 +36650,7 @@
         <v>189</v>
       </c>
       <c r="B381" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="C381" t="s">
         <v>68</v>
@@ -37840,7 +36715,7 @@
         <v>189</v>
       </c>
       <c r="B382" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="C382" t="s">
         <v>68</v>
@@ -37905,7 +36780,7 @@
         <v>189</v>
       </c>
       <c r="B383" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="C383" t="s">
         <v>68</v>
@@ -38425,7 +37300,7 @@
         <v>189</v>
       </c>
       <c r="B391" t="s">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="C391" t="s">
         <v>68</v>
@@ -38555,7 +37430,7 @@
         <v>189</v>
       </c>
       <c r="B393" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="C393" t="s">
         <v>68</v>
@@ -39010,7 +37885,7 @@
         <v>189</v>
       </c>
       <c r="B400" t="s">
-        <v>329</v>
+        <v>302</v>
       </c>
       <c r="C400" t="s">
         <v>68</v>
@@ -39270,7 +38145,7 @@
         <v>189</v>
       </c>
       <c r="B404" t="s">
-        <v>330</v>
+        <v>303</v>
       </c>
       <c r="C404" t="s">
         <v>68</v>
@@ -39335,7 +38210,7 @@
         <v>189</v>
       </c>
       <c r="B405" t="s">
-        <v>331</v>
+        <v>304</v>
       </c>
       <c r="C405" t="s">
         <v>68</v>
@@ -39400,7 +38275,7 @@
         <v>189</v>
       </c>
       <c r="B406" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="C406" t="s">
         <v>68</v>
@@ -39530,7 +38405,7 @@
         <v>189</v>
       </c>
       <c r="B408" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="C408" t="s">
         <v>68</v>
@@ -39660,7 +38535,7 @@
         <v>189</v>
       </c>
       <c r="B410" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="C410" t="s">
         <v>68</v>
@@ -39725,7 +38600,7 @@
         <v>189</v>
       </c>
       <c r="B411" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="C411" t="s">
         <v>68</v>
@@ -39985,7 +38860,7 @@
         <v>189</v>
       </c>
       <c r="B415" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="C415" t="s">
         <v>68</v>
@@ -40310,7 +39185,7 @@
         <v>189</v>
       </c>
       <c r="B420" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="C420" t="s">
         <v>68</v>
@@ -40440,7 +39315,7 @@
         <v>189</v>
       </c>
       <c r="B422" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="C422" t="s">
         <v>68</v>
@@ -40700,7 +39575,7 @@
         <v>189</v>
       </c>
       <c r="B426" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="C426" t="s">
         <v>68</v>
@@ -40765,7 +39640,7 @@
         <v>189</v>
       </c>
       <c r="B427" t="s">
-        <v>340</v>
+        <v>313</v>
       </c>
       <c r="C427" t="s">
         <v>68</v>
@@ -40833,7 +39708,7 @@
         <v>171</v>
       </c>
       <c r="C428" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D428" t="b">
         <v>1</v>
@@ -40898,7 +39773,7 @@
         <v>172</v>
       </c>
       <c r="C429" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D429" t="b">
         <v>1</v>
@@ -40963,7 +39838,7 @@
         <v>173</v>
       </c>
       <c r="C430" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D430" t="b">
         <v>1</v>
@@ -41025,10 +39900,10 @@
         <v>189</v>
       </c>
       <c r="B431" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="C431" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="D431" t="b">
         <v>0</v>
@@ -41101,19 +39976,19 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>342</v>
+        <v>315</v>
       </c>
       <c r="C1" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="D1" t="s">
-        <v>194</v>
+        <v>317</v>
       </c>
       <c r="E1" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="F1" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2">
@@ -41121,7 +39996,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="n">
@@ -41139,10 +40014,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C3" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="D3" t="n">
         <v>372</v>
@@ -41159,10 +40034,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C4" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="D4" t="n">
         <v>313</v>
@@ -41179,10 +40054,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C5" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="D5" t="n">
         <v>367</v>
@@ -41199,10 +40074,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="D6" t="n">
         <v>370</v>
@@ -41219,10 +40094,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C7" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D7" t="n">
         <v>382</v>
@@ -41239,10 +40114,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="D8" t="n">
         <v>308</v>
@@ -41259,10 +40134,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
         <v>311</v>
@@ -41279,10 +40154,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
         <v>311</v>
@@ -41299,10 +40174,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C11" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="D11" t="n">
         <v>311</v>
@@ -41319,10 +40194,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="D12" t="n">
         <v>311</v>
@@ -41339,10 +40214,10 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C13" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="D13" t="n">
         <v>311</v>
@@ -41359,10 +40234,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C14" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="D14" t="n">
         <v>311</v>
@@ -41379,10 +40254,10 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C15" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="D15" t="n">
         <v>311</v>
@@ -41399,10 +40274,10 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C16" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="D16" t="n">
         <v>311</v>
@@ -41419,10 +40294,10 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C17" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="D17" t="n">
         <v>311</v>
@@ -41439,10 +40314,10 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C18" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="D18" t="n">
         <v>311</v>
@@ -41459,10 +40334,10 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C19" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="D19" t="n">
         <v>311</v>
@@ -41479,10 +40354,10 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C20" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="D20" t="n">
         <v>311</v>
@@ -41499,10 +40374,10 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C21" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="D21" t="n">
         <v>311</v>
@@ -41519,10 +40394,10 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C22" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="D22" t="n">
         <v>311</v>
@@ -41539,10 +40414,10 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C23" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="D23" t="n">
         <v>311</v>
@@ -41559,10 +40434,10 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C24" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="D24" t="n">
         <v>311</v>
@@ -41579,10 +40454,10 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C25" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="D25" t="n">
         <v>311</v>
@@ -41599,10 +40474,10 @@
         <v>8</v>
       </c>
       <c r="B26" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C26" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="D26" t="n">
         <v>311</v>
@@ -41619,10 +40494,10 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C27" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="D27" t="n">
         <v>311</v>
@@ -41639,10 +40514,10 @@
         <v>8</v>
       </c>
       <c r="B28" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C28" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="D28" t="n">
         <v>311</v>
@@ -41659,7 +40534,7 @@
         <v>189</v>
       </c>
       <c r="B29" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="n">
@@ -41677,10 +40552,10 @@
         <v>189</v>
       </c>
       <c r="B30" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C30" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="D30" t="n">
         <v>341</v>
@@ -41697,10 +40572,10 @@
         <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C31" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="D31" t="n">
         <v>286</v>
@@ -41717,10 +40592,10 @@
         <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C32" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="D32" t="n">
         <v>334</v>
@@ -41737,10 +40612,10 @@
         <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C33" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="D33" t="n">
         <v>340</v>
@@ -41757,10 +40632,10 @@
         <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C34" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
       <c r="D34" t="n">
         <v>350</v>
@@ -41777,10 +40652,10 @@
         <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="C35" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="D35" t="n">
         <v>280</v>
@@ -41797,10 +40672,10 @@
         <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C36" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="D36" t="n">
         <v>285</v>
@@ -41817,10 +40692,10 @@
         <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C37" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="D37" t="n">
         <v>285</v>
@@ -41837,10 +40712,10 @@
         <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C38" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="D38" t="n">
         <v>285</v>
@@ -41857,10 +40732,10 @@
         <v>189</v>
       </c>
       <c r="B39" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C39" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="D39" t="n">
         <v>285</v>
@@ -41877,10 +40752,10 @@
         <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C40" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="D40" t="n">
         <v>285</v>
@@ -41897,10 +40772,10 @@
         <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C41" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="D41" t="n">
         <v>285</v>
@@ -41917,10 +40792,10 @@
         <v>189</v>
       </c>
       <c r="B42" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C42" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="D42" t="n">
         <v>285</v>
@@ -41937,10 +40812,10 @@
         <v>189</v>
       </c>
       <c r="B43" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C43" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="D43" t="n">
         <v>285</v>
@@ -41957,10 +40832,10 @@
         <v>189</v>
       </c>
       <c r="B44" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C44" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="D44" t="n">
         <v>285</v>
@@ -41977,10 +40852,10 @@
         <v>189</v>
       </c>
       <c r="B45" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C45" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="D45" t="n">
         <v>285</v>
@@ -41997,10 +40872,10 @@
         <v>189</v>
       </c>
       <c r="B46" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C46" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="D46" t="n">
         <v>285</v>
@@ -42017,10 +40892,10 @@
         <v>189</v>
       </c>
       <c r="B47" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C47" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="D47" t="n">
         <v>285</v>
@@ -42037,10 +40912,10 @@
         <v>189</v>
       </c>
       <c r="B48" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C48" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="D48" t="n">
         <v>285</v>
@@ -42057,10 +40932,10 @@
         <v>189</v>
       </c>
       <c r="B49" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C49" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="D49" t="n">
         <v>285</v>
@@ -42077,10 +40952,10 @@
         <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C50" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="D50" t="n">
         <v>285</v>
@@ -42097,10 +40972,10 @@
         <v>189</v>
       </c>
       <c r="B51" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C51" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="D51" t="n">
         <v>285</v>
@@ -42117,10 +40992,10 @@
         <v>189</v>
       </c>
       <c r="B52" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C52" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="D52" t="n">
         <v>285</v>
@@ -42137,10 +41012,10 @@
         <v>189</v>
       </c>
       <c r="B53" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C53" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="D53" t="n">
         <v>285</v>
@@ -42157,10 +41032,10 @@
         <v>189</v>
       </c>
       <c r="B54" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C54" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="D54" t="n">
         <v>285</v>
@@ -42177,10 +41052,10 @@
         <v>189</v>
       </c>
       <c r="B55" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="C55" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="D55" t="n">
         <v>285</v>
